--- a/test-files/graph-tests/different-sized-networks/52-genes-0-edges.xlsx
+++ b/test-files/graph-tests/different-sized-networks/52-genes-0-edges.xlsx
@@ -1,1447 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25725"/>
-  <workbookPr autoCompressPictures="0"/>
-  <bookViews>
-    <workbookView xWindow="460" yWindow="60" windowWidth="25140" windowHeight="14120"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="false"/>
   <sheets>
-    <sheet name="network" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="network" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="140001" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="365">
-  <si>
-    <t>FLO9</t>
-  </si>
-  <si>
-    <t>MMS4</t>
-  </si>
-  <si>
-    <t>FES1</t>
-  </si>
-  <si>
-    <t>EXO84</t>
-  </si>
-  <si>
-    <t>IML3</t>
-  </si>
-  <si>
-    <t>AIM3</t>
-  </si>
-  <si>
-    <t>CMD1</t>
-  </si>
-  <si>
-    <t>ALG1</t>
-  </si>
-  <si>
-    <t>CYC8</t>
-  </si>
-  <si>
-    <t>LYS2</t>
-  </si>
-  <si>
-    <t>MUD1</t>
-  </si>
-  <si>
-    <t>CBP6</t>
-  </si>
-  <si>
-    <t>GRS1</t>
-  </si>
-  <si>
-    <t>MRPL36</t>
-  </si>
-  <si>
-    <t>ATG14</t>
-  </si>
-  <si>
-    <t>CCZ1</t>
-  </si>
-  <si>
-    <t>AGP2</t>
-  </si>
-  <si>
-    <t>HSL7</t>
-  </si>
-  <si>
-    <t>CKS1</t>
-  </si>
-  <si>
-    <t>MEC1</t>
-  </si>
-  <si>
-    <t>IRA1</t>
-  </si>
-  <si>
-    <t>BMT2</t>
-  </si>
-  <si>
-    <t>MAK5</t>
-  </si>
-  <si>
-    <t>ADH5</t>
-  </si>
-  <si>
-    <t>MRPS9</t>
-  </si>
-  <si>
-    <t>ARA1</t>
-  </si>
-  <si>
-    <t>APD1</t>
-  </si>
-  <si>
-    <t>CNS1</t>
-  </si>
-  <si>
-    <t>ICS2</t>
-  </si>
-  <si>
-    <t>AMN1</t>
-  </si>
-  <si>
-    <t>IFA38</t>
-  </si>
-  <si>
-    <t>CDC28</t>
-  </si>
-  <si>
-    <t>EXO5</t>
-  </si>
-  <si>
-    <t>ARL1</t>
-  </si>
-  <si>
-    <t>ECM31</t>
-  </si>
-  <si>
-    <t>EHT1</t>
-  </si>
-  <si>
-    <t>FZO1</t>
-  </si>
-  <si>
-    <t>DTR1</t>
-  </si>
-  <si>
-    <t>MBA1</t>
-  </si>
-  <si>
-    <t>GDT1</t>
-  </si>
-  <si>
-    <t>MED8</t>
-  </si>
-  <si>
-    <t>AIM4</t>
-  </si>
-  <si>
-    <t>MSI1</t>
-  </si>
-  <si>
-    <t>KTR4</t>
-  </si>
-  <si>
-    <t>BEM1</t>
-  </si>
-  <si>
-    <t>DER1</t>
-  </si>
-  <si>
-    <t>MCM7</t>
-  </si>
-  <si>
-    <t>COS111</t>
-  </si>
-  <si>
-    <t>LDH1</t>
-  </si>
-  <si>
-    <t>KTR3</t>
-  </si>
-  <si>
-    <t>FTH1</t>
-  </si>
-  <si>
-    <t>DUR1</t>
-  </si>
-  <si>
-    <t>YER130C</t>
-  </si>
-  <si>
-    <t>YER184C</t>
-  </si>
-  <si>
-    <t>YFL052W</t>
-  </si>
-  <si>
-    <t>YGR067C</t>
-  </si>
-  <si>
-    <t>YJL206C</t>
-  </si>
-  <si>
-    <t>YKL222C</t>
-  </si>
-  <si>
-    <t>YLR278C</t>
-  </si>
-  <si>
-    <t>YNR063W</t>
-  </si>
-  <si>
-    <t>YPR015C</t>
-  </si>
-  <si>
-    <t>YPR022C</t>
-  </si>
-  <si>
-    <t>YPR196W</t>
-  </si>
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>Abf1</t>
-  </si>
-  <si>
-    <t>Aca1</t>
-  </si>
-  <si>
-    <t>Ace2</t>
-  </si>
-  <si>
-    <t>Ada2</t>
-  </si>
-  <si>
-    <t>Adr1</t>
-  </si>
-  <si>
-    <t>Aft1</t>
-  </si>
-  <si>
-    <t>Aft2</t>
-  </si>
-  <si>
-    <t>Arg80</t>
-  </si>
-  <si>
-    <t>Arg81</t>
-  </si>
-  <si>
-    <t>Arg82</t>
-  </si>
-  <si>
-    <t>Aro80</t>
-  </si>
-  <si>
-    <t>Arr1</t>
-  </si>
-  <si>
-    <t>Asf1</t>
-  </si>
-  <si>
-    <t>Asg1</t>
-  </si>
-  <si>
-    <t>Ash1</t>
-  </si>
-  <si>
-    <t>Ask10</t>
-  </si>
-  <si>
-    <t>Azf1</t>
-  </si>
-  <si>
-    <t>Bas1</t>
-  </si>
-  <si>
-    <t>Bdf2</t>
-  </si>
-  <si>
-    <t>Bye1</t>
-  </si>
-  <si>
-    <t>Cac2</t>
-  </si>
-  <si>
-    <t>Cad1</t>
-  </si>
-  <si>
-    <t>Caf4</t>
-  </si>
-  <si>
-    <t>Cat8</t>
-  </si>
-  <si>
-    <t>Cbf1</t>
-  </si>
-  <si>
-    <t>Cdc73</t>
-  </si>
-  <si>
-    <t>Cha4</t>
-  </si>
-  <si>
-    <t>Cin5</t>
-  </si>
-  <si>
-    <t>Crz1</t>
-  </si>
-  <si>
-    <t>Cse2</t>
-  </si>
-  <si>
-    <t>Cst6</t>
-  </si>
-  <si>
-    <t>Cyc8</t>
-  </si>
-  <si>
-    <t>Dal80</t>
-  </si>
-  <si>
-    <t>Dal81</t>
-  </si>
-  <si>
-    <t>Dal82</t>
-  </si>
-  <si>
-    <t>Dat1</t>
-  </si>
-  <si>
-    <t>Dig1</t>
-  </si>
-  <si>
-    <t>Dig2</t>
-  </si>
-  <si>
-    <t>Dot5</t>
-  </si>
-  <si>
-    <t>Dot6</t>
-  </si>
-  <si>
-    <t>Ecm22</t>
-  </si>
-  <si>
-    <t>Eds1</t>
-  </si>
-  <si>
-    <t>Ert1</t>
-  </si>
-  <si>
-    <t>Esa1</t>
-  </si>
-  <si>
-    <t>Esc2</t>
-  </si>
-  <si>
-    <t>Fhl1</t>
-  </si>
-  <si>
-    <t>Fkh1</t>
-  </si>
-  <si>
-    <t>Fkh2</t>
-  </si>
-  <si>
-    <t>Flo11</t>
-  </si>
-  <si>
-    <t>Flo8</t>
-  </si>
-  <si>
-    <t>Fzf1</t>
-  </si>
-  <si>
-    <t>Gal11</t>
-  </si>
-  <si>
-    <t>Gal3</t>
-  </si>
-  <si>
-    <t>Gal4</t>
-  </si>
-  <si>
-    <t>Gal80</t>
-  </si>
-  <si>
-    <t>Gat1</t>
-  </si>
-  <si>
-    <t>Gat3</t>
-  </si>
-  <si>
-    <t>Gat4</t>
-  </si>
-  <si>
-    <t>Gcn4</t>
-  </si>
-  <si>
-    <t>Gcr1</t>
-  </si>
-  <si>
-    <t>Gcr2</t>
-  </si>
-  <si>
-    <t>Gis1</t>
-  </si>
-  <si>
-    <t>Gis2</t>
-  </si>
-  <si>
-    <t>Gln3</t>
-  </si>
-  <si>
-    <t>Gsm1</t>
-  </si>
-  <si>
-    <t>Gts1</t>
-  </si>
-  <si>
-    <t>Gzf3</t>
-  </si>
-  <si>
-    <t>Haa1</t>
-  </si>
-  <si>
-    <t>Hac1</t>
-  </si>
-  <si>
-    <t>Hal9</t>
-  </si>
-  <si>
-    <t>Hat1</t>
-  </si>
-  <si>
-    <t>Hat2</t>
-  </si>
-  <si>
-    <t>Hcm1</t>
-  </si>
-  <si>
-    <t>Hda1</t>
-  </si>
-  <si>
-    <t>Hel2</t>
-  </si>
-  <si>
-    <t>Hfi1</t>
-  </si>
-  <si>
-    <t>Hir1</t>
-  </si>
-  <si>
-    <t>Hir2</t>
-  </si>
-  <si>
-    <t>Hir3</t>
-  </si>
-  <si>
-    <t>Hmo1</t>
-  </si>
-  <si>
-    <t>Hms1</t>
-  </si>
-  <si>
-    <t>Hms2</t>
-  </si>
-  <si>
-    <t>Hog1</t>
-  </si>
-  <si>
-    <t>Hot1</t>
-  </si>
-  <si>
-    <t>Hsf1</t>
-  </si>
-  <si>
-    <t>Hst1</t>
-  </si>
-  <si>
-    <t>Hst3</t>
-  </si>
-  <si>
-    <t>Hst4</t>
-  </si>
-  <si>
-    <t>Ifh1</t>
-  </si>
-  <si>
-    <t>Ime1</t>
-  </si>
-  <si>
-    <t>Ime4</t>
-  </si>
-  <si>
-    <t>Ino2</t>
-  </si>
-  <si>
-    <t>Ino4</t>
-  </si>
-  <si>
-    <t>Isw1</t>
-  </si>
-  <si>
-    <t>Isw2</t>
-  </si>
-  <si>
-    <t>Ixr1</t>
-  </si>
-  <si>
-    <t>Jhd1</t>
-  </si>
-  <si>
-    <t>Kar4</t>
-  </si>
-  <si>
-    <t>Kre33</t>
-  </si>
-  <si>
-    <t>Kss1</t>
-  </si>
-  <si>
-    <t>Leu3</t>
-  </si>
-  <si>
-    <t>Lys14</t>
-  </si>
-  <si>
-    <t>Mac1</t>
-  </si>
-  <si>
-    <t>Mal13</t>
-  </si>
-  <si>
-    <t>Mal33</t>
-  </si>
-  <si>
-    <t>Mal63</t>
-  </si>
-  <si>
-    <t>Mbf1</t>
-  </si>
-  <si>
-    <t>Mcm1</t>
-  </si>
-  <si>
-    <t>Mdl2</t>
-  </si>
-  <si>
-    <t>Mds3</t>
-  </si>
-  <si>
-    <t>Met18</t>
-  </si>
-  <si>
-    <t>Met28</t>
-  </si>
-  <si>
-    <t>Met31</t>
-  </si>
-  <si>
-    <t>Met32</t>
-  </si>
-  <si>
-    <t>Met4</t>
-  </si>
-  <si>
-    <t>Mga1</t>
-  </si>
-  <si>
-    <t>Mga2</t>
-  </si>
-  <si>
-    <t>Mig1</t>
-  </si>
-  <si>
-    <t>Mig2</t>
-  </si>
-  <si>
-    <t>Mig3</t>
-  </si>
-  <si>
-    <t>Mot2</t>
-  </si>
-  <si>
-    <t>Mot3</t>
-  </si>
-  <si>
-    <t>Msi1</t>
-  </si>
-  <si>
-    <t>Msn1</t>
-  </si>
-  <si>
-    <t>Msn2</t>
-  </si>
-  <si>
-    <t>Msn4</t>
-  </si>
-  <si>
-    <t>Mss11</t>
-  </si>
-  <si>
-    <t>Mth1</t>
-  </si>
-  <si>
-    <t>Ndd1</t>
-  </si>
-  <si>
-    <t>Ndt80</t>
-  </si>
-  <si>
-    <t>Ngg1</t>
-  </si>
-  <si>
-    <t>Nnf2</t>
-  </si>
-  <si>
-    <t>Not3</t>
-  </si>
-  <si>
-    <t>Nrg1</t>
-  </si>
-  <si>
-    <t>Nrg2</t>
-  </si>
-  <si>
-    <t>Nsi1</t>
-  </si>
-  <si>
-    <t>Nut1</t>
-  </si>
-  <si>
-    <t>Oaf1</t>
-  </si>
-  <si>
-    <t>Oaf3</t>
-  </si>
-  <si>
-    <t>Otu1</t>
-  </si>
-  <si>
-    <t>Pdc2</t>
-  </si>
-  <si>
-    <t>Pdr1</t>
-  </si>
-  <si>
-    <t>Pdr3</t>
-  </si>
-  <si>
-    <t>Pdr8</t>
-  </si>
-  <si>
-    <t>Pgd1</t>
-  </si>
-  <si>
-    <t>Phd1</t>
-  </si>
-  <si>
-    <t>Pho23</t>
-  </si>
-  <si>
-    <t>Pho2</t>
-  </si>
-  <si>
-    <t>Pho4</t>
-  </si>
-  <si>
-    <t>Pib2</t>
-  </si>
-  <si>
-    <t>Plm2</t>
-  </si>
-  <si>
-    <t>Pog1</t>
-  </si>
-  <si>
-    <t>Put3</t>
-  </si>
-  <si>
-    <t>Rco1</t>
-  </si>
-  <si>
-    <t>Rdr1</t>
-  </si>
-  <si>
-    <t>Rds1</t>
-  </si>
-  <si>
-    <t>Rds2</t>
-  </si>
-  <si>
-    <t>Rds3</t>
-  </si>
-  <si>
-    <t>Reb1</t>
-  </si>
-  <si>
-    <t>Rfx1</t>
-  </si>
-  <si>
-    <t>Rgm1</t>
-  </si>
-  <si>
-    <t>Rgt1</t>
-  </si>
-  <si>
-    <t>Rgt2</t>
-  </si>
-  <si>
-    <t>Ric1</t>
-  </si>
-  <si>
-    <t>Rif1</t>
-  </si>
-  <si>
-    <t>Rif2</t>
-  </si>
-  <si>
-    <t>Rim101</t>
-  </si>
-  <si>
-    <t>Rlf2</t>
-  </si>
-  <si>
-    <t>Rlm1</t>
-  </si>
-  <si>
-    <t>Rme1</t>
-  </si>
-  <si>
-    <t>Rox1</t>
-  </si>
-  <si>
-    <t>Rsc1</t>
-  </si>
-  <si>
-    <t>Rsc2</t>
-  </si>
-  <si>
-    <t>Rsc30</t>
-  </si>
-  <si>
-    <t>Rsf2</t>
-  </si>
-  <si>
-    <t>Rtf1</t>
-  </si>
-  <si>
-    <t>Rtg1</t>
-  </si>
-  <si>
-    <t>Rtg2</t>
-  </si>
-  <si>
-    <t>Rtg3</t>
-  </si>
-  <si>
-    <t>Rts2</t>
-  </si>
-  <si>
-    <t>Rtt107</t>
-  </si>
-  <si>
-    <t>Sas3</t>
-  </si>
-  <si>
-    <t>Sas4</t>
-  </si>
-  <si>
-    <t>Sas5</t>
-  </si>
-  <si>
-    <t>Sds3</t>
-  </si>
-  <si>
-    <t>Sef1</t>
-  </si>
-  <si>
-    <t>Set2</t>
-  </si>
-  <si>
-    <t>Sfl1</t>
-  </si>
-  <si>
-    <t>Sif2</t>
-  </si>
-  <si>
-    <t>Sin3</t>
-  </si>
-  <si>
-    <t>Sin4</t>
-  </si>
-  <si>
-    <t>Sir1</t>
-  </si>
-  <si>
-    <t>Sir2</t>
-  </si>
-  <si>
-    <t>Sir3</t>
-  </si>
-  <si>
-    <t>Skn7</t>
-  </si>
-  <si>
-    <t>Sko1</t>
-  </si>
-  <si>
-    <t>Smk1</t>
-  </si>
-  <si>
-    <t>Snf11</t>
-  </si>
-  <si>
-    <t>Snf1</t>
-  </si>
-  <si>
-    <t>Snf2</t>
-  </si>
-  <si>
-    <t>Snf5</t>
-  </si>
-  <si>
-    <t>Snf6</t>
-  </si>
-  <si>
-    <t>Snf7</t>
-  </si>
-  <si>
-    <t>Snt2</t>
-  </si>
-  <si>
-    <t>Sok2</t>
-  </si>
-  <si>
-    <t>Srb2</t>
-  </si>
-  <si>
-    <t>Srb5</t>
-  </si>
-  <si>
-    <t>Srb8</t>
-  </si>
-  <si>
-    <t>Srd1</t>
-  </si>
-  <si>
-    <t>Ssn2</t>
-  </si>
-  <si>
-    <t>Ssn3</t>
-  </si>
-  <si>
-    <t>Stb1</t>
-  </si>
-  <si>
-    <t>Stb2</t>
-  </si>
-  <si>
-    <t>Stb3</t>
-  </si>
-  <si>
-    <t>Stb4</t>
-  </si>
-  <si>
-    <t>Stb5</t>
-  </si>
-  <si>
-    <t>Stb6</t>
-  </si>
-  <si>
-    <t>Ste12</t>
-  </si>
-  <si>
-    <t>Sua7</t>
-  </si>
-  <si>
-    <t>Sum1</t>
-  </si>
-  <si>
-    <t>Sut1</t>
-  </si>
-  <si>
-    <t>Sut2</t>
-  </si>
-  <si>
-    <t>Swi3</t>
-  </si>
-  <si>
-    <t>Swi4</t>
-  </si>
-  <si>
-    <t>Swi5</t>
-  </si>
-  <si>
-    <t>Swi6</t>
-  </si>
-  <si>
-    <t>Taf14</t>
-  </si>
-  <si>
-    <t>Tbf1</t>
-  </si>
-  <si>
-    <t>Tbs1</t>
-  </si>
-  <si>
-    <t>Tda9</t>
-  </si>
-  <si>
-    <t>Tec1</t>
-  </si>
-  <si>
-    <t>Thi2</t>
-  </si>
-  <si>
-    <t>Thi3</t>
-  </si>
-  <si>
-    <t>Tho2</t>
-  </si>
-  <si>
-    <t>Tis11</t>
-  </si>
-  <si>
-    <t>Tod6</t>
-  </si>
-  <si>
-    <t>Tos4</t>
-  </si>
-  <si>
-    <t>Tos8</t>
-  </si>
-  <si>
-    <t>Tye7</t>
-  </si>
-  <si>
-    <t>Uga3</t>
-  </si>
-  <si>
-    <t>Uls1</t>
-  </si>
-  <si>
-    <t>Ume1</t>
-  </si>
-  <si>
-    <t>Ume6</t>
-  </si>
-  <si>
-    <t>Urc2</t>
-  </si>
-  <si>
-    <t>Ure2</t>
-  </si>
-  <si>
-    <t>Usv1</t>
-  </si>
-  <si>
-    <t>Vms1</t>
-  </si>
-  <si>
-    <t>War1</t>
-  </si>
-  <si>
-    <t>Wtm1</t>
-  </si>
-  <si>
-    <t>Wtm2</t>
-  </si>
-  <si>
-    <t>Yox1</t>
-  </si>
-  <si>
-    <t>Yrm1</t>
-  </si>
-  <si>
-    <t>Yrr1</t>
-  </si>
-  <si>
-    <t>Zds1</t>
-  </si>
-  <si>
-    <t>Cup2</t>
-  </si>
-  <si>
-    <t>Cup9</t>
-  </si>
-  <si>
-    <t>Elp6</t>
-  </si>
-  <si>
-    <t>Hap1</t>
-  </si>
-  <si>
-    <t>Hap2</t>
-  </si>
-  <si>
-    <t>Hap3</t>
-  </si>
-  <si>
-    <t>Hap4</t>
-  </si>
-  <si>
-    <t>Hap5</t>
-  </si>
-  <si>
-    <t>Hpa2</t>
-  </si>
-  <si>
-    <t>Hpc2</t>
-  </si>
-  <si>
-    <t>Imp2'</t>
-  </si>
-  <si>
-    <t>Mbp1</t>
-  </si>
-  <si>
-    <t>Opi1</t>
-  </si>
-  <si>
-    <t>Pip2</t>
-  </si>
-  <si>
-    <t>Pop2</t>
-  </si>
-  <si>
-    <t>Ppr1</t>
-  </si>
-  <si>
-    <t>Rap1</t>
-  </si>
-  <si>
-    <t>Rpd3</t>
-  </si>
-  <si>
-    <t>Rph1</t>
-  </si>
-  <si>
-    <t>Rpi1</t>
-  </si>
-  <si>
-    <t>Rpn10</t>
-  </si>
-  <si>
-    <t>Rpn4</t>
-  </si>
-  <si>
-    <t>Sfp1</t>
-  </si>
-  <si>
-    <t>Sip3</t>
-  </si>
-  <si>
-    <t>Sip4</t>
-  </si>
-  <si>
-    <t>Smp1</t>
-  </si>
-  <si>
-    <t>Sps18</t>
-  </si>
-  <si>
-    <t>Spt10</t>
-  </si>
-  <si>
-    <t>Spt20</t>
-  </si>
-  <si>
-    <t>Spt23</t>
-  </si>
-  <si>
-    <t>Spt2</t>
-  </si>
-  <si>
-    <t>Spt3</t>
-  </si>
-  <si>
-    <t>Spt4</t>
-  </si>
-  <si>
-    <t>Stp1</t>
-  </si>
-  <si>
-    <t>Stp2</t>
-  </si>
-  <si>
-    <t>Stp3</t>
-  </si>
-  <si>
-    <t>Stp4</t>
-  </si>
-  <si>
-    <t>Tup1</t>
-  </si>
-  <si>
-    <t>Upc2</t>
-  </si>
-  <si>
-    <t>Xbp1</t>
-  </si>
-  <si>
-    <t>Yap1</t>
-  </si>
-  <si>
-    <t>Yap3</t>
-  </si>
-  <si>
-    <t>Yap5</t>
-  </si>
-  <si>
-    <t>Yap6</t>
-  </si>
-  <si>
-    <t>Yap7</t>
-  </si>
-  <si>
-    <t>Yhp1</t>
-  </si>
-  <si>
-    <t>Zap1</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="21" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1449,225 +61,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="48">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="48">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="43" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="45" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="47" builtinId="9" hidden="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="44" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="46" builtinId="8" hidden="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -1816,20 +221,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1951,180 +352,218 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BA53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:53" ht="13">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" t="s">
-        <v>47</v>
-      </c>
-      <c r="U1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" t="s">
-        <v>45</v>
-      </c>
-      <c r="W1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:53">
-      <c r="A2" t="s">
-        <v>23</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ADH5</v>
+      </c>
+      <c r="C1" t="str">
+        <v>AGP2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>AIM3</v>
+      </c>
+      <c r="E1" t="str">
+        <v>AIM4</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ALG1</v>
+      </c>
+      <c r="G1" t="str">
+        <v>AMN1</v>
+      </c>
+      <c r="H1" t="str">
+        <v>APD1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>ARA1</v>
+      </c>
+      <c r="J1" t="str">
+        <v>ARL1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>ATG14</v>
+      </c>
+      <c r="L1" t="str">
+        <v>BEM1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>BMT2</v>
+      </c>
+      <c r="N1" t="str">
+        <v>CBP6</v>
+      </c>
+      <c r="O1" t="str">
+        <v>CCZ1</v>
+      </c>
+      <c r="P1" t="str">
+        <v>CDC28</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>CKS1</v>
+      </c>
+      <c r="R1" t="str">
+        <v>CMD1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>CNS1</v>
+      </c>
+      <c r="T1" t="str">
+        <v>COS111</v>
+      </c>
+      <c r="U1" t="str">
+        <v>CYC8</v>
+      </c>
+      <c r="V1" t="str">
+        <v>DER1</v>
+      </c>
+      <c r="W1" t="str">
+        <v>DTR1</v>
+      </c>
+      <c r="X1" t="str">
+        <v>DUR1</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>ECM31</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>EHT1</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>EXO5</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>EXO84</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>FES1</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>FLO9</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>FTH1</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>FZO1</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>GDT1</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>GRS1</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>HSL7</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>ICS2</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>IFA38</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>IML3</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>IRA1</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>KTR3</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>KTR4</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>LDH1</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>LYS2</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>MAK5</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>MBA1</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>MCM7</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>MEC1</v>
+      </c>
+      <c r="AV1" t="str">
+        <v>MED8</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>MMS4</v>
+      </c>
+      <c r="AX1" t="str">
+        <v>MRPL36</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>MRPS9</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>MSI1</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>MUD1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ADH5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2283,9 +722,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
-      <c r="A3" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AGP2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2444,9 +883,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53">
-      <c r="A4" t="s">
-        <v>5</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AIM3</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2605,9 +1044,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53">
-      <c r="A5" t="s">
-        <v>41</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AIM4</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2766,9 +1205,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53">
-      <c r="A6" t="s">
-        <v>7</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ALG1</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2927,9 +1366,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53">
-      <c r="A7" t="s">
-        <v>29</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AMN1</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3088,9 +1527,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53">
-      <c r="A8" t="s">
-        <v>26</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>APD1</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3249,9 +1688,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53">
-      <c r="A9" t="s">
-        <v>25</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ARA1</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3410,9 +1849,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53">
-      <c r="A10" t="s">
-        <v>33</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ARL1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3571,9 +2010,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53">
-      <c r="A11" t="s">
-        <v>14</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ATG14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3732,9 +2171,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53">
-      <c r="A12" t="s">
-        <v>44</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BEM1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3893,9 +2332,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53">
-      <c r="A13" t="s">
-        <v>21</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BMT2</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4054,9 +2493,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53">
-      <c r="A14" t="s">
-        <v>11</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CBP6</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4215,9 +2654,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53">
-      <c r="A15" t="s">
-        <v>15</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CCZ1</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4376,9 +2815,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53">
-      <c r="A16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CDC28</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4537,9 +2976,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
-      <c r="A17" t="s">
-        <v>18</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CKS1</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4698,9 +3137,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
-      <c r="A18" t="s">
-        <v>6</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CMD1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4859,9 +3298,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
-      <c r="A19" t="s">
-        <v>27</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CNS1</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5020,9 +3459,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
-      <c r="A20" t="s">
-        <v>47</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>COS111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5181,9 +3620,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
-      <c r="A21" t="s">
-        <v>8</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CYC8</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5342,9 +3781,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
-      <c r="A22" t="s">
-        <v>45</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>DER1</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5503,9 +3942,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:53">
-      <c r="A23" t="s">
-        <v>37</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>DTR1</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5664,9 +4103,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:53">
-      <c r="A24" t="s">
-        <v>51</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>DUR1</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5825,9 +4264,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:53">
-      <c r="A25" t="s">
-        <v>34</v>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>ECM31</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5986,9 +4425,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:53">
-      <c r="A26" t="s">
-        <v>35</v>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>EHT1</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6147,9 +4586,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:53">
-      <c r="A27" t="s">
-        <v>32</v>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>EXO5</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6308,9 +4747,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:53">
-      <c r="A28" t="s">
-        <v>3</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>EXO84</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6469,9 +4908,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:53">
-      <c r="A29" t="s">
-        <v>2</v>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>FES1</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6630,9 +5069,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:53">
-      <c r="A30" t="s">
-        <v>0</v>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>FLO9</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6791,9 +5230,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:53">
-      <c r="A31" t="s">
-        <v>50</v>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>FTH1</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6952,9 +5391,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:53">
-      <c r="A32" t="s">
-        <v>36</v>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>FZO1</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -7113,9 +5552,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:53">
-      <c r="A33" t="s">
-        <v>39</v>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>GDT1</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -7274,9 +5713,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:53">
-      <c r="A34" t="s">
-        <v>12</v>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>GRS1</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -7435,9 +5874,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:53">
-      <c r="A35" t="s">
-        <v>17</v>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HSL7</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -7596,9 +6035,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:53">
-      <c r="A36" t="s">
-        <v>28</v>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>ICS2</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -7757,9 +6196,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:53">
-      <c r="A37" t="s">
-        <v>30</v>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>IFA38</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -7918,9 +6357,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:53">
-      <c r="A38" t="s">
-        <v>4</v>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>IML3</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -8079,9 +6518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:53">
-      <c r="A39" t="s">
-        <v>20</v>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>IRA1</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -8240,9 +6679,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:53">
-      <c r="A40" t="s">
-        <v>49</v>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>KTR3</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -8401,9 +6840,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:53">
-      <c r="A41" t="s">
-        <v>43</v>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>KTR4</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -8562,9 +7001,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:53">
-      <c r="A42" t="s">
-        <v>48</v>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>LDH1</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -8723,9 +7162,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:53">
-      <c r="A43" t="s">
-        <v>9</v>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>LYS2</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -8884,9 +7323,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:53">
-      <c r="A44" t="s">
-        <v>22</v>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>MAK5</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -9045,9 +7484,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:53">
-      <c r="A45" t="s">
-        <v>38</v>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>MBA1</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -9206,9 +7645,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:53">
-      <c r="A46" t="s">
-        <v>46</v>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>MCM7</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -9367,9 +7806,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:53">
-      <c r="A47" t="s">
-        <v>19</v>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>MEC1</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -9528,9 +7967,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:53">
-      <c r="A48" t="s">
-        <v>40</v>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>MED8</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -9689,9 +8128,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:53">
-      <c r="A49" t="s">
-        <v>1</v>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>MMS4</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -9850,9 +8289,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:53">
-      <c r="A50" t="s">
-        <v>13</v>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>MRPL36</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -10011,9 +8450,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:53">
-      <c r="A51" t="s">
-        <v>24</v>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>MRPS9</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -10172,9 +8611,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:53">
-      <c r="A52" t="s">
-        <v>42</v>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>MSI1</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -10333,9 +8772,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:53">
-      <c r="A53" t="s">
-        <v>10</v>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>MUD1</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -10495,2835 +8934,2828 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:BA53"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B312"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>64</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Abf1</v>
       </c>
       <c r="B1" t="str">
         <f>UPPER(A1)</f>
         <v>ABF1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>65</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Aca1</v>
       </c>
       <c r="B2" t="str">
-        <f t="shared" ref="B2:B65" si="0">UPPER(A2)</f>
+        <f>UPPER(A2)</f>
         <v>ACA1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>66</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Ace2</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A3)</f>
         <v>ACE2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>67</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Ada2</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A4)</f>
         <v>ADA2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>68</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Adr1</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A5)</f>
         <v>ADR1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>69</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Aft1</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A6)</f>
         <v>AFT1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>70</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Aft2</v>
       </c>
       <c r="B7" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A7)</f>
         <v>AFT2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>71</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Arg80</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A8)</f>
         <v>ARG80</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>72</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Arg81</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A9)</f>
         <v>ARG81</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>73</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Arg82</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A10)</f>
         <v>ARG82</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>74</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Aro80</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A11)</f>
         <v>ARO80</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>75</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Arr1</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A12)</f>
         <v>ARR1</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>76</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Asf1</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A13)</f>
         <v>ASF1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>77</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Asg1</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A14)</f>
         <v>ASG1</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>78</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Ash1</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A15)</f>
         <v>ASH1</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>79</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Ask10</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A16)</f>
         <v>ASK10</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>80</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Azf1</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A17)</f>
         <v>AZF1</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>81</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Bas1</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A18)</f>
         <v>BAS1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>82</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Bdf2</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A19)</f>
         <v>BDF2</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>83</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Bye1</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A20)</f>
         <v>BYE1</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>84</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Cac2</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A21)</f>
         <v>CAC2</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>85</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Cad1</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A22)</f>
         <v>CAD1</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>86</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Caf4</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A23)</f>
         <v>CAF4</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>87</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Cat8</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A24)</f>
         <v>CAT8</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>88</v>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Cbf1</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A25)</f>
         <v>CBF1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>89</v>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Cdc73</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A26)</f>
         <v>CDC73</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>90</v>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Cha4</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A27)</f>
         <v>CHA4</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>91</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Cin5</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A28)</f>
         <v>CIN5</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>92</v>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Crz1</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A29)</f>
         <v>CRZ1</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>93</v>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Cse2</v>
       </c>
       <c r="B30" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A30)</f>
         <v>CSE2</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>94</v>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Cst6</v>
       </c>
       <c r="B31" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A31)</f>
         <v>CST6</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>318</v>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Cup2</v>
       </c>
       <c r="B32" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A32)</f>
         <v>CUP2</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>319</v>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Cup9</v>
       </c>
       <c r="B33" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A33)</f>
         <v>CUP9</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>95</v>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Cyc8</v>
       </c>
       <c r="B34" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A34)</f>
         <v>CYC8</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>96</v>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Dal80</v>
       </c>
       <c r="B35" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A35)</f>
         <v>DAL80</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>97</v>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Dal81</v>
       </c>
       <c r="B36" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A36)</f>
         <v>DAL81</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>98</v>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Dal82</v>
       </c>
       <c r="B37" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A37)</f>
         <v>DAL82</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>99</v>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Dat1</v>
       </c>
       <c r="B38" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A38)</f>
         <v>DAT1</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>100</v>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Dig1</v>
       </c>
       <c r="B39" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A39)</f>
         <v>DIG1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>101</v>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Dig2</v>
       </c>
       <c r="B40" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A40)</f>
         <v>DIG2</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>102</v>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Dot5</v>
       </c>
       <c r="B41" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A41)</f>
         <v>DOT5</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>103</v>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Dot6</v>
       </c>
       <c r="B42" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A42)</f>
         <v>DOT6</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>104</v>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Ecm22</v>
       </c>
       <c r="B43" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A43)</f>
         <v>ECM22</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>105</v>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Eds1</v>
       </c>
       <c r="B44" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A44)</f>
         <v>EDS1</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>320</v>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Elp6</v>
       </c>
       <c r="B45" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A45)</f>
         <v>ELP6</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>106</v>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Ert1</v>
       </c>
       <c r="B46" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A46)</f>
         <v>ERT1</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>107</v>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Esa1</v>
       </c>
       <c r="B47" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A47)</f>
         <v>ESA1</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>108</v>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Esc2</v>
       </c>
       <c r="B48" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A48)</f>
         <v>ESC2</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>109</v>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Fhl1</v>
       </c>
       <c r="B49" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A49)</f>
         <v>FHL1</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>110</v>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Fkh1</v>
       </c>
       <c r="B50" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A50)</f>
         <v>FKH1</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>111</v>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Fkh2</v>
       </c>
       <c r="B51" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A51)</f>
         <v>FKH2</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>112</v>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Flo11</v>
       </c>
       <c r="B52" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A52)</f>
         <v>FLO11</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>113</v>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Flo8</v>
       </c>
       <c r="B53" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A53)</f>
         <v>FLO8</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>114</v>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Fzf1</v>
       </c>
       <c r="B54" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A54)</f>
         <v>FZF1</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>115</v>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Gal11</v>
       </c>
       <c r="B55" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A55)</f>
         <v>GAL11</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>116</v>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Gal3</v>
       </c>
       <c r="B56" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A56)</f>
         <v>GAL3</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>117</v>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Gal4</v>
       </c>
       <c r="B57" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A57)</f>
         <v>GAL4</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>118</v>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Gal80</v>
       </c>
       <c r="B58" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A58)</f>
         <v>GAL80</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>119</v>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Gat1</v>
       </c>
       <c r="B59" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A59)</f>
         <v>GAT1</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>120</v>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Gat3</v>
       </c>
       <c r="B60" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A60)</f>
         <v>GAT3</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>121</v>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Gat4</v>
       </c>
       <c r="B61" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A61)</f>
         <v>GAT4</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>122</v>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Gcn4</v>
       </c>
       <c r="B62" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A62)</f>
         <v>GCN4</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>123</v>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Gcr1</v>
       </c>
       <c r="B63" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A63)</f>
         <v>GCR1</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>124</v>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Gcr2</v>
       </c>
       <c r="B64" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A64)</f>
         <v>GCR2</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>125</v>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Gis1</v>
       </c>
       <c r="B65" t="str">
-        <f t="shared" si="0"/>
+        <f>UPPER(A65)</f>
         <v>GIS1</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>126</v>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Gis2</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B129" si="1">UPPER(A66)</f>
+        <f>UPPER(A66)</f>
         <v>GIS2</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>127</v>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Gln3</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A67)</f>
         <v>GLN3</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>128</v>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Gsm1</v>
       </c>
       <c r="B68" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A68)</f>
         <v>GSM1</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>129</v>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Gts1</v>
       </c>
       <c r="B69" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A69)</f>
         <v>GTS1</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>130</v>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Gzf3</v>
       </c>
       <c r="B70" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A70)</f>
         <v>GZF3</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>131</v>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Haa1</v>
       </c>
       <c r="B71" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A71)</f>
         <v>HAA1</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>132</v>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Hac1</v>
       </c>
       <c r="B72" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A72)</f>
         <v>HAC1</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>133</v>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Hal9</v>
       </c>
       <c r="B73" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A73)</f>
         <v>HAL9</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>321</v>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Hap1</v>
       </c>
       <c r="B74" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A74)</f>
         <v>HAP1</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
-        <v>322</v>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Hap2</v>
       </c>
       <c r="B75" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A75)</f>
         <v>HAP2</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76" t="s">
-        <v>323</v>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Hap3</v>
       </c>
       <c r="B76" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A76)</f>
         <v>HAP3</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>324</v>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Hap4</v>
       </c>
       <c r="B77" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A77)</f>
         <v>HAP4</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>325</v>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Hap5</v>
       </c>
       <c r="B78" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A78)</f>
         <v>HAP5</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>134</v>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Hat1</v>
       </c>
       <c r="B79" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A79)</f>
         <v>HAT1</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>135</v>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Hat2</v>
       </c>
       <c r="B80" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A80)</f>
         <v>HAT2</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>136</v>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Hcm1</v>
       </c>
       <c r="B81" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A81)</f>
         <v>HCM1</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>137</v>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Hda1</v>
       </c>
       <c r="B82" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A82)</f>
         <v>HDA1</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>138</v>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Hel2</v>
       </c>
       <c r="B83" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A83)</f>
         <v>HEL2</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>139</v>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Hfi1</v>
       </c>
       <c r="B84" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A84)</f>
         <v>HFI1</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>140</v>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Hir1</v>
       </c>
       <c r="B85" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A85)</f>
         <v>HIR1</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>141</v>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Hir2</v>
       </c>
       <c r="B86" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A86)</f>
         <v>HIR2</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>142</v>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Hir3</v>
       </c>
       <c r="B87" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A87)</f>
         <v>HIR3</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>143</v>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Hmo1</v>
       </c>
       <c r="B88" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A88)</f>
         <v>HMO1</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>144</v>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Hms1</v>
       </c>
       <c r="B89" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A89)</f>
         <v>HMS1</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>145</v>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Hms2</v>
       </c>
       <c r="B90" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A90)</f>
         <v>HMS2</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>146</v>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Hog1</v>
       </c>
       <c r="B91" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A91)</f>
         <v>HOG1</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>147</v>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Hot1</v>
       </c>
       <c r="B92" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A92)</f>
         <v>HOT1</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
-        <v>326</v>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Hpa2</v>
       </c>
       <c r="B93" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A93)</f>
         <v>HPA2</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>327</v>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Hpc2</v>
       </c>
       <c r="B94" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A94)</f>
         <v>HPC2</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>148</v>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Hsf1</v>
       </c>
       <c r="B95" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A95)</f>
         <v>HSF1</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>149</v>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Hst1</v>
       </c>
       <c r="B96" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A96)</f>
         <v>HST1</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>150</v>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Hst3</v>
       </c>
       <c r="B97" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A97)</f>
         <v>HST3</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>151</v>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Hst4</v>
       </c>
       <c r="B98" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A98)</f>
         <v>HST4</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>152</v>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Ifh1</v>
       </c>
       <c r="B99" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A99)</f>
         <v>IFH1</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>153</v>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Ime1</v>
       </c>
       <c r="B100" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A100)</f>
         <v>IME1</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>154</v>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Ime4</v>
       </c>
       <c r="B101" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A101)</f>
         <v>IME4</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>328</v>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Imp2'</v>
       </c>
       <c r="B102" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A102)</f>
         <v>IMP2'</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>155</v>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Ino2</v>
       </c>
       <c r="B103" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A103)</f>
         <v>INO2</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>156</v>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Ino4</v>
       </c>
       <c r="B104" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A104)</f>
         <v>INO4</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
-      <c r="A105" t="s">
-        <v>157</v>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Isw1</v>
       </c>
       <c r="B105" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A105)</f>
         <v>ISW1</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
-      <c r="A106" t="s">
-        <v>158</v>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Isw2</v>
       </c>
       <c r="B106" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A106)</f>
         <v>ISW2</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
-      <c r="A107" t="s">
-        <v>159</v>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Ixr1</v>
       </c>
       <c r="B107" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A107)</f>
         <v>IXR1</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
-      <c r="A108" t="s">
-        <v>160</v>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Jhd1</v>
       </c>
       <c r="B108" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A108)</f>
         <v>JHD1</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="A109" t="s">
-        <v>161</v>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Kar4</v>
       </c>
       <c r="B109" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A109)</f>
         <v>KAR4</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
-      <c r="A110" t="s">
-        <v>162</v>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Kre33</v>
       </c>
       <c r="B110" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A110)</f>
         <v>KRE33</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
-      <c r="A111" t="s">
-        <v>163</v>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Kss1</v>
       </c>
       <c r="B111" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A111)</f>
         <v>KSS1</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
-      <c r="A112" t="s">
-        <v>164</v>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Leu3</v>
       </c>
       <c r="B112" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A112)</f>
         <v>LEU3</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
-        <v>165</v>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Lys14</v>
       </c>
       <c r="B113" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A113)</f>
         <v>LYS14</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114" t="s">
-        <v>166</v>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Mac1</v>
       </c>
       <c r="B114" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A114)</f>
         <v>MAC1</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="A115" t="s">
-        <v>167</v>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Mal13</v>
       </c>
       <c r="B115" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A115)</f>
         <v>MAL13</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
-      <c r="A116" t="s">
-        <v>168</v>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Mal33</v>
       </c>
       <c r="B116" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A116)</f>
         <v>MAL33</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
-      <c r="A117" t="s">
-        <v>169</v>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Mal63</v>
       </c>
       <c r="B117" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A117)</f>
         <v>MAL63</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
-      <c r="A118" t="s">
-        <v>170</v>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Mbf1</v>
       </c>
       <c r="B118" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A118)</f>
         <v>MBF1</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
-      <c r="A119" t="s">
-        <v>329</v>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Mbp1</v>
       </c>
       <c r="B119" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A119)</f>
         <v>MBP1</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>171</v>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Mcm1</v>
       </c>
       <c r="B120" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A120)</f>
         <v>MCM1</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
-      <c r="A121" t="s">
-        <v>172</v>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Mdl2</v>
       </c>
       <c r="B121" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A121)</f>
         <v>MDL2</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
-      <c r="A122" t="s">
-        <v>173</v>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Mds3</v>
       </c>
       <c r="B122" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A122)</f>
         <v>MDS3</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
-      <c r="A123" t="s">
-        <v>174</v>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Met18</v>
       </c>
       <c r="B123" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A123)</f>
         <v>MET18</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
-      <c r="A124" t="s">
-        <v>175</v>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Met28</v>
       </c>
       <c r="B124" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A124)</f>
         <v>MET28</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
-      <c r="A125" t="s">
-        <v>176</v>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Met31</v>
       </c>
       <c r="B125" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A125)</f>
         <v>MET31</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>177</v>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Met32</v>
       </c>
       <c r="B126" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A126)</f>
         <v>MET32</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
-      <c r="A127" t="s">
-        <v>178</v>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Met4</v>
       </c>
       <c r="B127" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A127)</f>
         <v>MET4</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
-      <c r="A128" t="s">
-        <v>179</v>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Mga1</v>
       </c>
       <c r="B128" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A128)</f>
         <v>MGA1</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
-      <c r="A129" t="s">
-        <v>180</v>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Mga2</v>
       </c>
       <c r="B129" t="str">
-        <f t="shared" si="1"/>
+        <f>UPPER(A129)</f>
         <v>MGA2</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
-      <c r="A130" t="s">
-        <v>181</v>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Mig1</v>
       </c>
       <c r="B130" t="str">
-        <f t="shared" ref="B130:B193" si="2">UPPER(A130)</f>
+        <f>UPPER(A130)</f>
         <v>MIG1</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="A131" t="s">
-        <v>182</v>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Mig2</v>
       </c>
       <c r="B131" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A131)</f>
         <v>MIG2</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
-      <c r="A132" t="s">
-        <v>183</v>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Mig3</v>
       </c>
       <c r="B132" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A132)</f>
         <v>MIG3</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>184</v>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Mot2</v>
       </c>
       <c r="B133" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A133)</f>
         <v>MOT2</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>185</v>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Mot3</v>
       </c>
       <c r="B134" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A134)</f>
         <v>MOT3</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>186</v>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Msi1</v>
       </c>
       <c r="B135" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A135)</f>
         <v>MSI1</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
-        <v>187</v>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Msn1</v>
       </c>
       <c r="B136" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A136)</f>
         <v>MSN1</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>188</v>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Msn2</v>
       </c>
       <c r="B137" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A137)</f>
         <v>MSN2</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
-      <c r="A138" t="s">
-        <v>189</v>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Msn4</v>
       </c>
       <c r="B138" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A138)</f>
         <v>MSN4</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>190</v>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Mss11</v>
       </c>
       <c r="B139" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A139)</f>
         <v>MSS11</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>191</v>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Mth1</v>
       </c>
       <c r="B140" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A140)</f>
         <v>MTH1</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>192</v>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Ndd1</v>
       </c>
       <c r="B141" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A141)</f>
         <v>NDD1</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
-      <c r="A142" t="s">
-        <v>193</v>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Ndt80</v>
       </c>
       <c r="B142" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A142)</f>
         <v>NDT80</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
-        <v>194</v>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Ngg1</v>
       </c>
       <c r="B143" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A143)</f>
         <v>NGG1</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>195</v>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Nnf2</v>
       </c>
       <c r="B144" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A144)</f>
         <v>NNF2</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>196</v>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Not3</v>
       </c>
       <c r="B145" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A145)</f>
         <v>NOT3</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>197</v>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Nrg1</v>
       </c>
       <c r="B146" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A146)</f>
         <v>NRG1</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>198</v>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Nrg2</v>
       </c>
       <c r="B147" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A147)</f>
         <v>NRG2</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>199</v>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Nsi1</v>
       </c>
       <c r="B148" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A148)</f>
         <v>NSI1</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>200</v>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Nut1</v>
       </c>
       <c r="B149" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A149)</f>
         <v>NUT1</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>201</v>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Oaf1</v>
       </c>
       <c r="B150" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A150)</f>
         <v>OAF1</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>202</v>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Oaf3</v>
       </c>
       <c r="B151" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A151)</f>
         <v>OAF3</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>330</v>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Opi1</v>
       </c>
       <c r="B152" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A152)</f>
         <v>OPI1</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>203</v>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Otu1</v>
       </c>
       <c r="B153" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A153)</f>
         <v>OTU1</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
-      <c r="A154" t="s">
-        <v>204</v>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>Pdc2</v>
       </c>
       <c r="B154" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A154)</f>
         <v>PDC2</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
-      <c r="A155" t="s">
-        <v>205</v>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Pdr1</v>
       </c>
       <c r="B155" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A155)</f>
         <v>PDR1</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>206</v>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Pdr3</v>
       </c>
       <c r="B156" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A156)</f>
         <v>PDR3</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>207</v>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Pdr8</v>
       </c>
       <c r="B157" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A157)</f>
         <v>PDR8</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>208</v>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Pgd1</v>
       </c>
       <c r="B158" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A158)</f>
         <v>PGD1</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>209</v>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Phd1</v>
       </c>
       <c r="B159" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A159)</f>
         <v>PHD1</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>210</v>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Pho23</v>
       </c>
       <c r="B160" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A160)</f>
         <v>PHO23</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
-      <c r="A161" t="s">
-        <v>211</v>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>Pho2</v>
       </c>
       <c r="B161" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A161)</f>
         <v>PHO2</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>212</v>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Pho4</v>
       </c>
       <c r="B162" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A162)</f>
         <v>PHO4</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
-      <c r="A163" t="s">
-        <v>213</v>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Pib2</v>
       </c>
       <c r="B163" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A163)</f>
         <v>PIB2</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>331</v>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Pip2</v>
       </c>
       <c r="B164" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A164)</f>
         <v>PIP2</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
-      <c r="A165" t="s">
-        <v>214</v>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Plm2</v>
       </c>
       <c r="B165" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A165)</f>
         <v>PLM2</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
-      <c r="A166" t="s">
-        <v>215</v>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Pog1</v>
       </c>
       <c r="B166" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A166)</f>
         <v>POG1</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
-      <c r="A167" t="s">
-        <v>332</v>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Pop2</v>
       </c>
       <c r="B167" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A167)</f>
         <v>POP2</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
-        <v>333</v>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Ppr1</v>
       </c>
       <c r="B168" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A168)</f>
         <v>PPR1</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
-      <c r="A169" t="s">
-        <v>216</v>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>Put3</v>
       </c>
       <c r="B169" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A169)</f>
         <v>PUT3</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
-      <c r="A170" t="s">
-        <v>334</v>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Rap1</v>
       </c>
       <c r="B170" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A170)</f>
         <v>RAP1</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
-      <c r="A171" t="s">
-        <v>217</v>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Rco1</v>
       </c>
       <c r="B171" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A171)</f>
         <v>RCO1</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
-      <c r="A172" t="s">
-        <v>218</v>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Rdr1</v>
       </c>
       <c r="B172" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A172)</f>
         <v>RDR1</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
-      <c r="A173" t="s">
-        <v>219</v>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>Rds1</v>
       </c>
       <c r="B173" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A173)</f>
         <v>RDS1</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
-      <c r="A174" t="s">
-        <v>220</v>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>Rds2</v>
       </c>
       <c r="B174" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A174)</f>
         <v>RDS2</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
-      <c r="A175" t="s">
-        <v>221</v>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>Rds3</v>
       </c>
       <c r="B175" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A175)</f>
         <v>RDS3</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
-      <c r="A176" t="s">
-        <v>222</v>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>Reb1</v>
       </c>
       <c r="B176" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A176)</f>
         <v>REB1</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
-      <c r="A177" t="s">
-        <v>223</v>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Rfx1</v>
       </c>
       <c r="B177" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A177)</f>
         <v>RFX1</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
-      <c r="A178" t="s">
-        <v>224</v>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Rgm1</v>
       </c>
       <c r="B178" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A178)</f>
         <v>RGM1</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
-      <c r="A179" t="s">
-        <v>225</v>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Rgt1</v>
       </c>
       <c r="B179" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A179)</f>
         <v>RGT1</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
-      <c r="A180" t="s">
-        <v>226</v>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Rgt2</v>
       </c>
       <c r="B180" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A180)</f>
         <v>RGT2</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
-      <c r="A181" t="s">
-        <v>227</v>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Ric1</v>
       </c>
       <c r="B181" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A181)</f>
         <v>RIC1</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
-      <c r="A182" t="s">
-        <v>228</v>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Rif1</v>
       </c>
       <c r="B182" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A182)</f>
         <v>RIF1</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
-      <c r="A183" t="s">
-        <v>229</v>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Rif2</v>
       </c>
       <c r="B183" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A183)</f>
         <v>RIF2</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
-      <c r="A184" t="s">
-        <v>230</v>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Rim101</v>
       </c>
       <c r="B184" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A184)</f>
         <v>RIM101</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
-      <c r="A185" t="s">
-        <v>231</v>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Rlf2</v>
       </c>
       <c r="B185" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A185)</f>
         <v>RLF2</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
-      <c r="A186" t="s">
-        <v>232</v>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Rlm1</v>
       </c>
       <c r="B186" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A186)</f>
         <v>RLM1</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
-      <c r="A187" t="s">
-        <v>233</v>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Rme1</v>
       </c>
       <c r="B187" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A187)</f>
         <v>RME1</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
-      <c r="A188" t="s">
-        <v>234</v>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Rox1</v>
       </c>
       <c r="B188" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A188)</f>
         <v>ROX1</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
-      <c r="A189" t="s">
-        <v>335</v>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>Rpd3</v>
       </c>
       <c r="B189" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A189)</f>
         <v>RPD3</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
-      <c r="A190" t="s">
-        <v>336</v>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Rph1</v>
       </c>
       <c r="B190" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A190)</f>
         <v>RPH1</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
-      <c r="A191" t="s">
-        <v>337</v>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Rpi1</v>
       </c>
       <c r="B191" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A191)</f>
         <v>RPI1</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
-      <c r="A192" t="s">
-        <v>338</v>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Rpn10</v>
       </c>
       <c r="B192" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A192)</f>
         <v>RPN10</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
-      <c r="A193" t="s">
-        <v>339</v>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Rpn4</v>
       </c>
       <c r="B193" t="str">
-        <f t="shared" si="2"/>
+        <f>UPPER(A193)</f>
         <v>RPN4</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
-      <c r="A194" t="s">
-        <v>235</v>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Rsc1</v>
       </c>
       <c r="B194" t="str">
-        <f t="shared" ref="B194:B257" si="3">UPPER(A194)</f>
+        <f>UPPER(A194)</f>
         <v>RSC1</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
-      <c r="A195" t="s">
-        <v>236</v>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Rsc2</v>
       </c>
       <c r="B195" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A195)</f>
         <v>RSC2</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
-      <c r="A196" t="s">
-        <v>237</v>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Rsc30</v>
       </c>
       <c r="B196" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A196)</f>
         <v>RSC30</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
-      <c r="A197" t="s">
-        <v>238</v>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Rsf2</v>
       </c>
       <c r="B197" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A197)</f>
         <v>RSF2</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
-      <c r="A198" t="s">
-        <v>239</v>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Rtf1</v>
       </c>
       <c r="B198" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A198)</f>
         <v>RTF1</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
-      <c r="A199" t="s">
-        <v>240</v>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Rtg1</v>
       </c>
       <c r="B199" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A199)</f>
         <v>RTG1</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
-      <c r="A200" t="s">
-        <v>241</v>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Rtg2</v>
       </c>
       <c r="B200" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A200)</f>
         <v>RTG2</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
-      <c r="A201" t="s">
-        <v>242</v>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Rtg3</v>
       </c>
       <c r="B201" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A201)</f>
         <v>RTG3</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
-      <c r="A202" t="s">
-        <v>243</v>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Rts2</v>
       </c>
       <c r="B202" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A202)</f>
         <v>RTS2</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
-      <c r="A203" t="s">
-        <v>244</v>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Rtt107</v>
       </c>
       <c r="B203" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A203)</f>
         <v>RTT107</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
-      <c r="A204" t="s">
-        <v>245</v>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Sas3</v>
       </c>
       <c r="B204" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A204)</f>
         <v>SAS3</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
-      <c r="A205" t="s">
-        <v>246</v>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Sas4</v>
       </c>
       <c r="B205" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A205)</f>
         <v>SAS4</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
-      <c r="A206" t="s">
-        <v>247</v>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Sas5</v>
       </c>
       <c r="B206" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A206)</f>
         <v>SAS5</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
-      <c r="A207" t="s">
-        <v>248</v>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Sds3</v>
       </c>
       <c r="B207" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A207)</f>
         <v>SDS3</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
-      <c r="A208" t="s">
-        <v>249</v>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Sef1</v>
       </c>
       <c r="B208" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A208)</f>
         <v>SEF1</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
-      <c r="A209" t="s">
-        <v>250</v>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Set2</v>
       </c>
       <c r="B209" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A209)</f>
         <v>SET2</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
-      <c r="A210" t="s">
-        <v>251</v>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Sfl1</v>
       </c>
       <c r="B210" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A210)</f>
         <v>SFL1</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
-      <c r="A211" t="s">
-        <v>340</v>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Sfp1</v>
       </c>
       <c r="B211" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A211)</f>
         <v>SFP1</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
-      <c r="A212" t="s">
-        <v>252</v>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Sif2</v>
       </c>
       <c r="B212" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A212)</f>
         <v>SIF2</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
-      <c r="A213" t="s">
-        <v>253</v>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Sin3</v>
       </c>
       <c r="B213" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A213)</f>
         <v>SIN3</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
-      <c r="A214" t="s">
-        <v>254</v>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Sin4</v>
       </c>
       <c r="B214" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A214)</f>
         <v>SIN4</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
-      <c r="A215" t="s">
-        <v>341</v>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Sip3</v>
       </c>
       <c r="B215" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A215)</f>
         <v>SIP3</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
-      <c r="A216" t="s">
-        <v>342</v>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Sip4</v>
       </c>
       <c r="B216" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A216)</f>
         <v>SIP4</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
-      <c r="A217" t="s">
-        <v>255</v>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Sir1</v>
       </c>
       <c r="B217" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A217)</f>
         <v>SIR1</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
-      <c r="A218" t="s">
-        <v>256</v>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Sir2</v>
       </c>
       <c r="B218" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A218)</f>
         <v>SIR2</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
-      <c r="A219" t="s">
-        <v>257</v>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Sir3</v>
       </c>
       <c r="B219" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A219)</f>
         <v>SIR3</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
-      <c r="A220" t="s">
-        <v>258</v>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Skn7</v>
       </c>
       <c r="B220" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A220)</f>
         <v>SKN7</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
-      <c r="A221" t="s">
-        <v>259</v>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Sko1</v>
       </c>
       <c r="B221" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A221)</f>
         <v>SKO1</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
-      <c r="A222" t="s">
-        <v>260</v>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Smk1</v>
       </c>
       <c r="B222" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A222)</f>
         <v>SMK1</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
-      <c r="A223" t="s">
-        <v>343</v>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Smp1</v>
       </c>
       <c r="B223" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A223)</f>
         <v>SMP1</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
-      <c r="A224" t="s">
-        <v>261</v>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>Snf11</v>
       </c>
       <c r="B224" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A224)</f>
         <v>SNF11</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
-      <c r="A225" t="s">
-        <v>262</v>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Snf1</v>
       </c>
       <c r="B225" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A225)</f>
         <v>SNF1</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
-      <c r="A226" t="s">
-        <v>263</v>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Snf2</v>
       </c>
       <c r="B226" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A226)</f>
         <v>SNF2</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
-      <c r="A227" t="s">
-        <v>264</v>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Snf5</v>
       </c>
       <c r="B227" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A227)</f>
         <v>SNF5</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
-      <c r="A228" t="s">
-        <v>265</v>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Snf6</v>
       </c>
       <c r="B228" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A228)</f>
         <v>SNF6</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
-      <c r="A229" t="s">
-        <v>266</v>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Snf7</v>
       </c>
       <c r="B229" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A229)</f>
         <v>SNF7</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
-      <c r="A230" t="s">
-        <v>267</v>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Snt2</v>
       </c>
       <c r="B230" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A230)</f>
         <v>SNT2</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
-      <c r="A231" t="s">
-        <v>268</v>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Sok2</v>
       </c>
       <c r="B231" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A231)</f>
         <v>SOK2</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
-      <c r="A232" t="s">
-        <v>344</v>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Sps18</v>
       </c>
       <c r="B232" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A232)</f>
         <v>SPS18</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
-      <c r="A233" t="s">
-        <v>345</v>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Spt10</v>
       </c>
       <c r="B233" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A233)</f>
         <v>SPT10</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
-      <c r="A234" t="s">
-        <v>346</v>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>Spt20</v>
       </c>
       <c r="B234" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A234)</f>
         <v>SPT20</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
-      <c r="A235" t="s">
-        <v>347</v>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Spt23</v>
       </c>
       <c r="B235" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A235)</f>
         <v>SPT23</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
-      <c r="A236" t="s">
-        <v>348</v>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Spt2</v>
       </c>
       <c r="B236" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A236)</f>
         <v>SPT2</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
-      <c r="A237" t="s">
-        <v>349</v>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Spt3</v>
       </c>
       <c r="B237" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A237)</f>
         <v>SPT3</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
-      <c r="A238" t="s">
-        <v>350</v>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Spt4</v>
       </c>
       <c r="B238" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A238)</f>
         <v>SPT4</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
-      <c r="A239" t="s">
-        <v>269</v>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Srb2</v>
       </c>
       <c r="B239" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A239)</f>
         <v>SRB2</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
-      <c r="A240" t="s">
-        <v>270</v>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Srb5</v>
       </c>
       <c r="B240" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A240)</f>
         <v>SRB5</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
-      <c r="A241" t="s">
-        <v>271</v>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Srb8</v>
       </c>
       <c r="B241" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A241)</f>
         <v>SRB8</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
-      <c r="A242" t="s">
-        <v>272</v>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Srd1</v>
       </c>
       <c r="B242" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A242)</f>
         <v>SRD1</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
-      <c r="A243" t="s">
-        <v>273</v>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Ssn2</v>
       </c>
       <c r="B243" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A243)</f>
         <v>SSN2</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
-      <c r="A244" t="s">
-        <v>274</v>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>Ssn3</v>
       </c>
       <c r="B244" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A244)</f>
         <v>SSN3</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
-      <c r="A245" t="s">
-        <v>275</v>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Stb1</v>
       </c>
       <c r="B245" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A245)</f>
         <v>STB1</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
-      <c r="A246" t="s">
-        <v>276</v>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Stb2</v>
       </c>
       <c r="B246" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A246)</f>
         <v>STB2</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
-      <c r="A247" t="s">
-        <v>277</v>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Stb3</v>
       </c>
       <c r="B247" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A247)</f>
         <v>STB3</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
-      <c r="A248" t="s">
-        <v>278</v>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Stb4</v>
       </c>
       <c r="B248" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A248)</f>
         <v>STB4</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
-      <c r="A249" t="s">
-        <v>279</v>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Stb5</v>
       </c>
       <c r="B249" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A249)</f>
         <v>STB5</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
-      <c r="A250" t="s">
-        <v>280</v>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Stb6</v>
       </c>
       <c r="B250" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A250)</f>
         <v>STB6</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
-      <c r="A251" t="s">
-        <v>281</v>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Ste12</v>
       </c>
       <c r="B251" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A251)</f>
         <v>STE12</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
-      <c r="A252" t="s">
-        <v>351</v>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Stp1</v>
       </c>
       <c r="B252" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A252)</f>
         <v>STP1</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
-      <c r="A253" t="s">
-        <v>352</v>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Stp2</v>
       </c>
       <c r="B253" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A253)</f>
         <v>STP2</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
-      <c r="A254" t="s">
-        <v>353</v>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Stp3</v>
       </c>
       <c r="B254" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A254)</f>
         <v>STP3</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
-      <c r="A255" t="s">
-        <v>354</v>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Stp4</v>
       </c>
       <c r="B255" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A255)</f>
         <v>STP4</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
-      <c r="A256" t="s">
-        <v>282</v>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Sua7</v>
       </c>
       <c r="B256" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A256)</f>
         <v>SUA7</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
-      <c r="A257" t="s">
-        <v>283</v>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Sum1</v>
       </c>
       <c r="B257" t="str">
-        <f t="shared" si="3"/>
+        <f>UPPER(A257)</f>
         <v>SUM1</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
-      <c r="A258" t="s">
-        <v>284</v>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Sut1</v>
       </c>
       <c r="B258" t="str">
-        <f t="shared" ref="B258:B312" si="4">UPPER(A258)</f>
+        <f>UPPER(A258)</f>
         <v>SUT1</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
-      <c r="A259" t="s">
-        <v>285</v>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Sut2</v>
       </c>
       <c r="B259" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A259)</f>
         <v>SUT2</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
-      <c r="A260" t="s">
-        <v>286</v>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Swi3</v>
       </c>
       <c r="B260" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A260)</f>
         <v>SWI3</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
-      <c r="A261" t="s">
-        <v>287</v>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Swi4</v>
       </c>
       <c r="B261" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A261)</f>
         <v>SWI4</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
-      <c r="A262" t="s">
-        <v>288</v>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Swi5</v>
       </c>
       <c r="B262" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A262)</f>
         <v>SWI5</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
-      <c r="A263" t="s">
-        <v>289</v>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Swi6</v>
       </c>
       <c r="B263" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A263)</f>
         <v>SWI6</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
-      <c r="A264" t="s">
-        <v>290</v>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Taf14</v>
       </c>
       <c r="B264" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A264)</f>
         <v>TAF14</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
-      <c r="A265" t="s">
-        <v>291</v>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Tbf1</v>
       </c>
       <c r="B265" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A265)</f>
         <v>TBF1</v>
       </c>
     </row>
-    <row r="266" spans="1:2">
-      <c r="A266" t="s">
-        <v>292</v>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Tbs1</v>
       </c>
       <c r="B266" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A266)</f>
         <v>TBS1</v>
       </c>
     </row>
-    <row r="267" spans="1:2">
-      <c r="A267" t="s">
-        <v>293</v>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Tda9</v>
       </c>
       <c r="B267" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A267)</f>
         <v>TDA9</v>
       </c>
     </row>
-    <row r="268" spans="1:2">
-      <c r="A268" t="s">
-        <v>294</v>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Tec1</v>
       </c>
       <c r="B268" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A268)</f>
         <v>TEC1</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
-      <c r="A269" t="s">
-        <v>295</v>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Thi2</v>
       </c>
       <c r="B269" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A269)</f>
         <v>THI2</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
-      <c r="A270" t="s">
-        <v>296</v>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Thi3</v>
       </c>
       <c r="B270" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A270)</f>
         <v>THI3</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
-      <c r="A271" t="s">
-        <v>297</v>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tho2</v>
       </c>
       <c r="B271" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A271)</f>
         <v>THO2</v>
       </c>
     </row>
-    <row r="272" spans="1:2">
-      <c r="A272" t="s">
-        <v>298</v>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>Tis11</v>
       </c>
       <c r="B272" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A272)</f>
         <v>TIS11</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
-      <c r="A273" t="s">
-        <v>299</v>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Tod6</v>
       </c>
       <c r="B273" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A273)</f>
         <v>TOD6</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
-      <c r="A274" t="s">
-        <v>300</v>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Tos4</v>
       </c>
       <c r="B274" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A274)</f>
         <v>TOS4</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
-      <c r="A275" t="s">
-        <v>301</v>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Tos8</v>
       </c>
       <c r="B275" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A275)</f>
         <v>TOS8</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
-      <c r="A276" t="s">
-        <v>355</v>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Tup1</v>
       </c>
       <c r="B276" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A276)</f>
         <v>TUP1</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
-      <c r="A277" t="s">
-        <v>302</v>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Tye7</v>
       </c>
       <c r="B277" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A277)</f>
         <v>TYE7</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
-      <c r="A278" t="s">
-        <v>303</v>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Uga3</v>
       </c>
       <c r="B278" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A278)</f>
         <v>UGA3</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
-      <c r="A279" t="s">
-        <v>304</v>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>Uls1</v>
       </c>
       <c r="B279" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A279)</f>
         <v>ULS1</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
-      <c r="A280" t="s">
-        <v>305</v>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>Ume1</v>
       </c>
       <c r="B280" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A280)</f>
         <v>UME1</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
-      <c r="A281" t="s">
-        <v>306</v>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Ume6</v>
       </c>
       <c r="B281" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A281)</f>
         <v>UME6</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
-      <c r="A282" t="s">
-        <v>356</v>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Upc2</v>
       </c>
       <c r="B282" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A282)</f>
         <v>UPC2</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
-      <c r="A283" t="s">
-        <v>307</v>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>Urc2</v>
       </c>
       <c r="B283" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A283)</f>
         <v>URC2</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
-      <c r="A284" t="s">
-        <v>308</v>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Ure2</v>
       </c>
       <c r="B284" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A284)</f>
         <v>URE2</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
-      <c r="A285" t="s">
-        <v>309</v>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>Usv1</v>
       </c>
       <c r="B285" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A285)</f>
         <v>USV1</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
-      <c r="A286" t="s">
-        <v>310</v>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Vms1</v>
       </c>
       <c r="B286" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A286)</f>
         <v>VMS1</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
-      <c r="A287" t="s">
-        <v>311</v>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>War1</v>
       </c>
       <c r="B287" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A287)</f>
         <v>WAR1</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
-      <c r="A288" t="s">
-        <v>312</v>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Wtm1</v>
       </c>
       <c r="B288" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A288)</f>
         <v>WTM1</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
-      <c r="A289" t="s">
-        <v>313</v>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Wtm2</v>
       </c>
       <c r="B289" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A289)</f>
         <v>WTM2</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
-      <c r="A290" t="s">
-        <v>357</v>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Xbp1</v>
       </c>
       <c r="B290" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A290)</f>
         <v>XBP1</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
-      <c r="A291" t="s">
-        <v>358</v>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Yap1</v>
       </c>
       <c r="B291" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A291)</f>
         <v>YAP1</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
-      <c r="A292" t="s">
-        <v>359</v>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Yap3</v>
       </c>
       <c r="B292" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A292)</f>
         <v>YAP3</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
-      <c r="A293" t="s">
-        <v>360</v>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Yap5</v>
       </c>
       <c r="B293" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A293)</f>
         <v>YAP5</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
-      <c r="A294" t="s">
-        <v>361</v>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Yap6</v>
       </c>
       <c r="B294" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A294)</f>
         <v>YAP6</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
-      <c r="A295" t="s">
-        <v>362</v>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Yap7</v>
       </c>
       <c r="B295" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A295)</f>
         <v>YAP7</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
-      <c r="A296" t="s">
-        <v>52</v>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>YER130C</v>
       </c>
       <c r="B296" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A296)</f>
         <v>YER130C</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
-      <c r="A297" t="s">
-        <v>53</v>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>YER184C</v>
       </c>
       <c r="B297" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A297)</f>
         <v>YER184C</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
-      <c r="A298" t="s">
-        <v>54</v>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>YFL052W</v>
       </c>
       <c r="B298" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A298)</f>
         <v>YFL052W</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
-      <c r="A299" t="s">
-        <v>55</v>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>YGR067C</v>
       </c>
       <c r="B299" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A299)</f>
         <v>YGR067C</v>
       </c>
     </row>
-    <row r="300" spans="1:2">
-      <c r="A300" t="s">
-        <v>363</v>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Yhp1</v>
       </c>
       <c r="B300" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A300)</f>
         <v>YHP1</v>
       </c>
     </row>
-    <row r="301" spans="1:2">
-      <c r="A301" t="s">
-        <v>56</v>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>YJL206C</v>
       </c>
       <c r="B301" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A301)</f>
         <v>YJL206C</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
-      <c r="A302" t="s">
-        <v>57</v>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>YKL222C</v>
       </c>
       <c r="B302" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A302)</f>
         <v>YKL222C</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
-      <c r="A303" t="s">
-        <v>58</v>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>YLR278C</v>
       </c>
       <c r="B303" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A303)</f>
         <v>YLR278C</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
-      <c r="A304" t="s">
-        <v>59</v>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>YNR063W</v>
       </c>
       <c r="B304" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A304)</f>
         <v>YNR063W</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
-      <c r="A305" t="s">
-        <v>314</v>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Yox1</v>
       </c>
       <c r="B305" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A305)</f>
         <v>YOX1</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
-      <c r="A306" t="s">
-        <v>60</v>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>YPR015C</v>
       </c>
       <c r="B306" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A306)</f>
         <v>YPR015C</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
-      <c r="A307" t="s">
-        <v>61</v>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>YPR022C</v>
       </c>
       <c r="B307" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A307)</f>
         <v>YPR022C</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
-      <c r="A308" t="s">
-        <v>62</v>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>YPR196W</v>
       </c>
       <c r="B308" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A308)</f>
         <v>YPR196W</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
-      <c r="A309" t="s">
-        <v>315</v>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Yrm1</v>
       </c>
       <c r="B309" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A309)</f>
         <v>YRM1</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
-      <c r="A310" t="s">
-        <v>316</v>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Yrr1</v>
       </c>
       <c r="B310" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A310)</f>
         <v>YRR1</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
-      <c r="A311" t="s">
-        <v>364</v>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>Zap1</v>
       </c>
       <c r="B311" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A311)</f>
         <v>ZAP1</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
-      <c r="A312" t="s">
-        <v>317</v>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>Zds1</v>
       </c>
       <c r="B312" t="str">
-        <f t="shared" si="4"/>
+        <f>UPPER(A312)</f>
         <v>ZDS1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B312"/>
+  </ignoredErrors>
 </worksheet>
 </file>